--- a/articles/yyyymmdd_stockmemo.xlsx
+++ b/articles/yyyymmdd_stockmemo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df63a93e45125bfa/Documents/zenn-contents/public/articles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{534248A1-53E3-4A35-8B78-4CC3CF13077E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{534248A1-53E3-4A35-8B78-4CC3CF13077E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1FE040E-89CB-47C3-940D-E8A5BEBC8204}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3B376C1F-CDE0-4DAE-B15D-C1F4F0EB3929}"/>
+    <workbookView xWindow="3765" yWindow="3765" windowWidth="21600" windowHeight="11295" xr2:uid="{3B376C1F-CDE0-4DAE-B15D-C1F4F0EB3929}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="50">
   <si>
     <t xml:space="preserve"> コード </t>
   </si>
@@ -87,172 +87,19 @@
     <t xml:space="preserve">     ロング     </t>
   </si>
   <si>
-    <t>関税警戒で&lt;br&gt;上値重い&lt;br&gt;レンジ</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> レンジの&lt;br&gt;下限狙い </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 住友林業           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">レンジ          </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 特S窓開けで&lt;br&gt;パニック </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PPIHD              </t>
-  </si>
-  <si>
     <t xml:space="preserve">    ショート    </t>
   </si>
   <si>
-    <t xml:space="preserve"> 高値圏の稲穂 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 稲葉製作所         </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CupWithHandle&lt;br&gt;＆窓埋め </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ブリジストン       </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 大幅安翌日寄付&lt;br&gt;での混乱に&lt;br&gt;巻き込まれた </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 急上昇と急落の&lt;br&gt;スピード感に&lt;br&gt;乗れなかった </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 日東紡績           </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CupWithHandle </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> バウンド前で&lt;br&gt;下限狙い </t>
-  </si>
-  <si>
     <t xml:space="preserve"> 三菱重工業         </t>
   </si>
   <si>
-    <t xml:space="preserve"> 高値圏の稲穂型 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">上値目線&lt;br&gt;レンジ  </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 反発ライン前で&lt;br&gt;ライン見誤り </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SBIHD              </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 大幅下落後の&lt;br&gt;反発 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 塩野義製薬         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">レンジ&lt;br&gt;上限付近  </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CupWithHandle&lt;br&gt;エントリーミス </t>
-  </si>
-  <si>
     <t xml:space="preserve"> オリンパス         </t>
   </si>
   <si>
-    <t xml:space="preserve"> レンジ上限付近&lt;br&gt;ライン見誤り </t>
-  </si>
-  <si>
     <t xml:space="preserve"> キャノン           </t>
   </si>
   <si>
-    <t xml:space="preserve">上値が重い&lt;br&gt;レンジ  </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 底値付近&lt;br&gt;仕手株で読めず </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 寄付時下落後&lt;br&gt;の上昇</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 東洋建設           </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 上抜け&lt;br&gt;上昇狙い</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 暴落価格付近&lt;br&gt;レンジ下端&lt;br&gt;狙い</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 上抜け&lt;br&gt;上昇狙い&lt;br&gt;地固め後の&lt;br&gt;押目買い</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 東邦チタ           </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 急上昇後の&lt;br&gt;稲穂型</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 豊田通商           </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 急上昇後の&lt;br&gt;急降下&lt;br&gt;成り行き&lt;br&gt;エントリー</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 成り行き&lt;br&gt;エントリー相殺</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 宮地エンジン       </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 高値圏の稲穂型</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> バウンド前で&lt;br&gt;下限狙い</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NTT                </t>
-  </si>
-  <si>
-    <t xml:space="preserve">      配当      </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  </t>
-  </si>
-  <si>
     <t xml:space="preserve"> 応用地質           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">上値が重い&lt;br&gt;レンジ </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ライン上抜け  </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 新明和工業         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 古河電機工業       </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 高値圏で撃ち&lt;br&gt;落される&lt;br&gt;場面狙い  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">レンジ&lt;br&gt;高値付近  </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 高値圏の&lt;br&gt;稲穂型（終盤）</t>
   </si>
   <si>
     <t>ロング</t>
@@ -275,6 +122,81 @@
   <si>
     <t>ショート</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 押し目買い</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     07XX </t>
+  </si>
+  <si>
+    <t xml:space="preserve">上昇        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> レンジ&lt;br&gt;だまし後の&lt;br&gt;上抜け</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 下端反発狙い</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 古野電機           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 急上昇後の&lt;br&gt;下落</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> レンジ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 積水ハウス         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> exitタイ&lt;br&gt;ミング逃し</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 武田製薬           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> レンジ上限</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ヤマックス         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 出来高少ない</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 古野電気           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 高値圏&lt;br&gt;勢い減少</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 損切ライン&lt;br&gt;設定ミス</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 下限狙い</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> アスクル           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 下落狙い&lt;br&gt;反発(損)切</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 富士通             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 下限狙い&lt;br&gt;下落(損)切</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 寿スピリッツ       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 下限狙い&lt;br&gt;反発損切</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 日本航空           </t>
   </si>
 </sst>
 </file>
@@ -638,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E56617F-AC17-47B0-8938-540D65EDC3F0}">
-  <dimension ref="B2:Q34"/>
+  <dimension ref="B2:Q23"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.4">
@@ -668,7 +590,7 @@
       </c>
       <c r="O2">
         <f>SUM(D4:D49)</f>
-        <v>33550</v>
+        <v>13620</v>
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.4">
@@ -697,39 +619,15 @@
         <v>13</v>
       </c>
       <c r="P3" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="Q3" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.4">
-      <c r="B4">
-        <v>7752</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4">
-        <v>-2200</v>
-      </c>
-      <c r="E4">
-        <v>530</v>
-      </c>
-      <c r="F4">
-        <v>602</v>
-      </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" t="s">
-        <v>17</v>
-      </c>
       <c r="O4" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="P4">
         <f>COUNTIFS(G4:G50, "*ロング*", D4:D50, "&gt;0")</f>
@@ -737,431 +635,381 @@
       </c>
       <c r="Q4">
         <f>COUNTIFS(G4:G50, "*ロング*", D4:D50, "&lt;0")</f>
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.4">
-      <c r="B5">
-        <v>1911</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5">
-        <v>-3700</v>
-      </c>
-      <c r="E5">
-        <v>602</v>
-      </c>
-      <c r="F5">
-        <v>602</v>
-      </c>
-      <c r="G5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" t="s">
-        <v>20</v>
-      </c>
       <c r="O5" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="P5">
         <f>COUNTIFS(G4:G50, "*ショート*", D4:D50, "&gt;0")</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q5">
         <f>COUNTIFS(G4:G50, "*ショート*", D4:D50, "&lt;0")</f>
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B6">
-        <v>7532</v>
+        <v>7733</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D6">
-        <v>4600</v>
+        <v>-2000</v>
       </c>
       <c r="E6">
-        <v>603</v>
-      </c>
-      <c r="F6">
-        <v>603</v>
+        <v>701</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B7">
-        <v>3421</v>
+        <v>7752</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D7">
-        <v>400</v>
+        <v>-1950</v>
       </c>
       <c r="E7">
-        <v>603</v>
+        <v>701</v>
       </c>
       <c r="F7">
-        <v>603</v>
+        <v>702</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B8">
-        <v>5108</v>
+        <v>7751</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D8">
-        <v>-900</v>
+        <v>-1400</v>
       </c>
       <c r="E8">
-        <v>603</v>
+        <v>701</v>
       </c>
       <c r="F8">
-        <v>603</v>
+        <v>701</v>
       </c>
       <c r="G8" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B9">
-        <v>5108</v>
+        <v>6814</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D9">
-        <v>-1180</v>
+        <v>4500</v>
       </c>
       <c r="E9">
-        <v>603</v>
+        <v>701</v>
       </c>
       <c r="F9">
-        <v>603</v>
+        <v>701</v>
       </c>
       <c r="G9" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H9" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B10">
-        <v>3110</v>
+        <v>6814</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="E10">
-        <v>604</v>
+        <v>701</v>
       </c>
       <c r="F10">
-        <v>604</v>
+        <v>701</v>
       </c>
       <c r="G10" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H10" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B11">
-        <v>5108</v>
+        <v>7752</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D11">
-        <v>-800</v>
+        <v>3650</v>
       </c>
       <c r="E11">
-        <v>605</v>
+        <v>702</v>
       </c>
       <c r="F11">
-        <v>605</v>
+        <v>703</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="I11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B12">
-        <v>7011</v>
+        <v>1928</v>
       </c>
       <c r="C12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12">
+        <v>-800</v>
+      </c>
+      <c r="E12">
+        <v>702</v>
+      </c>
+      <c r="F12">
+        <v>702</v>
+      </c>
+      <c r="G12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" t="s">
         <v>32</v>
       </c>
-      <c r="D12">
-        <v>2800</v>
-      </c>
-      <c r="E12">
-        <v>605</v>
-      </c>
-      <c r="F12">
-        <v>605</v>
-      </c>
-      <c r="G12" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" t="s">
-        <v>19</v>
-      </c>
       <c r="I12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B13">
-        <v>7752</v>
+        <v>4502</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D13">
-        <v>-2000</v>
+        <v>3220</v>
       </c>
       <c r="E13">
-        <v>605</v>
+        <v>703</v>
       </c>
       <c r="F13">
-        <v>606</v>
+        <v>703</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B14">
-        <v>8473</v>
+        <v>5285</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14">
-        <v>-900</v>
+        <v>-3000</v>
       </c>
       <c r="E14">
-        <v>610</v>
+        <v>707</v>
       </c>
       <c r="F14">
-        <v>610</v>
+        <v>707</v>
       </c>
       <c r="G14" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I14" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B15">
-        <v>5108</v>
+        <v>6814</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D15">
-        <v>16100</v>
+        <v>4000</v>
       </c>
       <c r="E15">
-        <v>610</v>
+        <v>707</v>
       </c>
       <c r="F15">
-        <v>612</v>
+        <v>707</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I15" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B16">
-        <v>4507</v>
+        <v>7011</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D16">
-        <v>300</v>
+        <v>-1700</v>
       </c>
       <c r="E16">
-        <v>612</v>
+        <v>707</v>
       </c>
       <c r="F16">
-        <v>612</v>
+        <v>707</v>
       </c>
       <c r="G16" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H16" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="I16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B17">
-        <v>4507</v>
+        <v>9755</v>
       </c>
       <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17">
+        <v>-200</v>
+      </c>
+      <c r="E17">
+        <v>707</v>
+      </c>
+      <c r="F17">
+        <v>707</v>
+      </c>
+      <c r="G17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" t="s">
         <v>38</v>
-      </c>
-      <c r="D17">
-        <v>2350</v>
-      </c>
-      <c r="E17">
-        <v>612</v>
-      </c>
-      <c r="F17">
-        <v>612</v>
-      </c>
-      <c r="G17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H17" t="s">
-        <v>39</v>
-      </c>
-      <c r="I17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B18">
-        <v>7733</v>
-      </c>
-      <c r="C18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18">
-        <v>850</v>
-      </c>
-      <c r="E18">
-        <v>612</v>
-      </c>
-      <c r="F18">
-        <v>613</v>
-      </c>
-      <c r="G18" t="s">
-        <v>22</v>
-      </c>
-      <c r="H18" t="s">
-        <v>39</v>
-      </c>
-      <c r="I18" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B19">
-        <v>7751</v>
+        <v>2678</v>
       </c>
       <c r="C19" t="s">
         <v>43</v>
       </c>
       <c r="D19">
-        <v>-1700</v>
+        <v>800</v>
       </c>
       <c r="E19">
-        <v>616</v>
+        <v>707</v>
       </c>
       <c r="F19">
-        <v>616</v>
+        <v>708</v>
       </c>
       <c r="G19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H19" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" t="s">
         <v>44</v>
-      </c>
-      <c r="I19" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B20">
-        <v>7751</v>
+        <v>6702</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D20">
-        <v>-3070</v>
+        <v>500</v>
       </c>
       <c r="E20">
-        <v>616</v>
+        <v>709</v>
       </c>
       <c r="F20">
-        <v>617</v>
+        <v>709</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I20" t="s">
         <v>46</v>
@@ -1169,25 +1017,25 @@
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B21">
-        <v>1890</v>
+        <v>2222</v>
       </c>
       <c r="C21" t="s">
         <v>47</v>
       </c>
       <c r="D21">
-        <v>-1500</v>
+        <v>-1050</v>
       </c>
       <c r="E21">
-        <v>616</v>
+        <v>709</v>
       </c>
       <c r="F21">
-        <v>617</v>
+        <v>709</v>
       </c>
       <c r="G21" t="s">
         <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I21" t="s">
         <v>48</v>
@@ -1195,340 +1043,54 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B22">
-        <v>7752</v>
+        <v>2222</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D22">
-        <v>5200</v>
+        <v>4700</v>
       </c>
       <c r="E22">
-        <v>616</v>
+        <v>709</v>
       </c>
       <c r="F22">
-        <v>627</v>
+        <v>710</v>
       </c>
       <c r="G22" t="s">
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I22" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B23">
-        <v>1890</v>
+        <v>9201</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D23">
-        <v>-700</v>
+        <v>850</v>
       </c>
       <c r="E23">
-        <v>618</v>
+        <v>710</v>
       </c>
       <c r="F23">
-        <v>625</v>
+        <v>710</v>
       </c>
       <c r="G23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H23" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I23" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B24">
-        <v>5727</v>
-      </c>
-      <c r="C24" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24">
-        <v>1700</v>
-      </c>
-      <c r="E24">
-        <v>619</v>
-      </c>
-      <c r="F24">
-        <v>619</v>
-      </c>
-      <c r="G24" t="s">
-        <v>22</v>
-      </c>
-      <c r="H24" t="s">
-        <v>44</v>
-      </c>
-      <c r="I24" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B25">
-        <v>8015</v>
-      </c>
-      <c r="C25" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25">
-        <v>220</v>
-      </c>
-      <c r="E25">
-        <v>620</v>
-      </c>
-      <c r="F25">
-        <v>620</v>
-      </c>
-      <c r="G25" t="s">
-        <v>22</v>
-      </c>
-      <c r="H25" t="s">
-        <v>44</v>
-      </c>
-      <c r="I25" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B26">
-        <v>8015</v>
-      </c>
-      <c r="C26" t="s">
-        <v>53</v>
-      </c>
-      <c r="D26">
-        <v>700</v>
-      </c>
-      <c r="E26">
-        <v>620</v>
-      </c>
-      <c r="F26">
-        <v>620</v>
-      </c>
-      <c r="G26" t="s">
-        <v>22</v>
-      </c>
-      <c r="H26" t="s">
-        <v>44</v>
-      </c>
-      <c r="I26" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B27">
-        <v>3431</v>
-      </c>
-      <c r="C27" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27">
-        <v>-800</v>
-      </c>
-      <c r="E27">
-        <v>620</v>
-      </c>
-      <c r="F27">
-        <v>620</v>
-      </c>
-      <c r="G27" t="s">
-        <v>22</v>
-      </c>
-      <c r="H27" t="s">
-        <v>44</v>
-      </c>
-      <c r="I27" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B28">
-        <v>7751</v>
-      </c>
-      <c r="C28" t="s">
-        <v>43</v>
-      </c>
-      <c r="D28">
-        <v>-1500</v>
-      </c>
-      <c r="E28">
-        <v>623</v>
-      </c>
-      <c r="F28">
-        <v>623</v>
-      </c>
-      <c r="G28" t="s">
-        <v>15</v>
-      </c>
-      <c r="H28" t="s">
-        <v>44</v>
-      </c>
-      <c r="I28" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B29">
-        <v>9432</v>
-      </c>
-      <c r="C29" t="s">
-        <v>59</v>
-      </c>
-      <c r="D29">
-        <v>5180</v>
-      </c>
-      <c r="E29">
-        <v>620</v>
-      </c>
-      <c r="F29">
-        <v>620</v>
-      </c>
-      <c r="G29" t="s">
-        <v>60</v>
-      </c>
-      <c r="H29" t="s">
-        <v>61</v>
-      </c>
-      <c r="I29" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B30">
-        <v>9755</v>
-      </c>
-      <c r="C30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D30">
-        <v>2600</v>
-      </c>
-      <c r="E30">
-        <v>625</v>
-      </c>
-      <c r="F30">
-        <v>625</v>
-      </c>
-      <c r="G30" t="s">
-        <v>15</v>
-      </c>
-      <c r="H30" t="s">
-        <v>64</v>
-      </c>
-      <c r="I30" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B31">
-        <v>7724</v>
-      </c>
-      <c r="C31" t="s">
-        <v>66</v>
-      </c>
-      <c r="D31">
-        <v>-800</v>
-      </c>
-      <c r="E31">
-        <v>626</v>
-      </c>
-      <c r="F31">
-        <v>626</v>
-      </c>
-      <c r="G31" t="s">
-        <v>22</v>
-      </c>
-      <c r="H31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I31" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B32">
-        <v>5801</v>
-      </c>
-      <c r="C32" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32">
-        <v>2800</v>
-      </c>
-      <c r="E32">
-        <v>627</v>
-      </c>
-      <c r="F32">
-        <v>627</v>
-      </c>
-      <c r="G32" t="s">
-        <v>22</v>
-      </c>
-      <c r="H32" t="s">
-        <v>61</v>
-      </c>
-      <c r="I32" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B33">
-        <v>1890</v>
-      </c>
-      <c r="C33" t="s">
-        <v>47</v>
-      </c>
-      <c r="D33">
-        <v>-800</v>
-      </c>
-      <c r="E33">
-        <v>630</v>
-      </c>
-      <c r="F33">
-        <v>630</v>
-      </c>
-      <c r="G33" t="s">
-        <v>22</v>
-      </c>
-      <c r="H33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I33" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B34">
-        <v>5801</v>
-      </c>
-      <c r="C34" t="s">
-        <v>68</v>
-      </c>
-      <c r="D34">
-        <v>6300</v>
-      </c>
-      <c r="E34">
-        <v>630</v>
-      </c>
-      <c r="F34">
-        <v>630</v>
-      </c>
-      <c r="G34" t="s">
-        <v>22</v>
-      </c>
-      <c r="H34" t="s">
-        <v>61</v>
-      </c>
-      <c r="I34" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/articles/yyyymmdd_stockmemo.xlsx
+++ b/articles/yyyymmdd_stockmemo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df63a93e45125bfa/Documents/zenn-contents/public/articles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{534248A1-53E3-4A35-8B78-4CC3CF13077E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1FE040E-89CB-47C3-940D-E8A5BEBC8204}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{534248A1-53E3-4A35-8B78-4CC3CF13077E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{145F813A-78C6-4DC9-9A74-8429BCC317CA}"/>
   <bookViews>
-    <workbookView xWindow="3765" yWindow="3765" windowWidth="21600" windowHeight="11295" xr2:uid="{3B376C1F-CDE0-4DAE-B15D-C1F4F0EB3929}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{3B376C1F-CDE0-4DAE-B15D-C1F4F0EB3929}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="59">
   <si>
     <t xml:space="preserve"> コード </t>
   </si>
@@ -197,6 +197,33 @@
   </si>
   <si>
     <t xml:space="preserve"> 日本航空           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 双日               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 200株&lt;br&gt;高値圏&lt;br&gt;勢い減少</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 日立製作所         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 三井物産           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 三共               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> アイシン           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> QPS                </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 日本特殊陶業       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> レゾナック         </t>
   </si>
 </sst>
 </file>
@@ -261,6 +288,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -560,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E56617F-AC17-47B0-8938-540D65EDC3F0}">
-  <dimension ref="B2:Q23"/>
+  <dimension ref="B2:Q32"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.4">
@@ -590,7 +621,7 @@
       </c>
       <c r="O2">
         <f>SUM(D4:D49)</f>
-        <v>13620</v>
+        <v>11784</v>
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.4">
@@ -631,11 +662,11 @@
       </c>
       <c r="P4">
         <f>COUNTIFS(G4:G50, "*ロング*", D4:D50, "&gt;0")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q4">
         <f>COUNTIFS(G4:G50, "*ロング*", D4:D50, "&lt;0")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.4">
@@ -644,11 +675,11 @@
       </c>
       <c r="P5">
         <f>COUNTIFS(G4:G50, "*ショート*", D4:D50, "&gt;0")</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q5">
         <f>COUNTIFS(G4:G50, "*ショート*", D4:D50, "&lt;0")</f>
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.4">
@@ -963,6 +994,32 @@
         <v>38</v>
       </c>
     </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B18">
+        <v>1928</v>
+      </c>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18">
+        <v>900</v>
+      </c>
+      <c r="E18">
+        <v>707</v>
+      </c>
+      <c r="F18">
+        <v>711</v>
+      </c>
+      <c r="G18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" t="s">
+        <v>42</v>
+      </c>
+    </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B19">
         <v>2678</v>
@@ -1091,6 +1148,240 @@
       </c>
       <c r="I23" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B24">
+        <v>2768</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24">
+        <v>1114</v>
+      </c>
+      <c r="E24">
+        <v>711</v>
+      </c>
+      <c r="F24">
+        <v>711</v>
+      </c>
+      <c r="G24" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B25">
+        <v>6501</v>
+      </c>
+      <c r="C25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25">
+        <v>-2900</v>
+      </c>
+      <c r="E25">
+        <v>711</v>
+      </c>
+      <c r="F25">
+        <v>711</v>
+      </c>
+      <c r="G25" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B26">
+        <v>8031</v>
+      </c>
+      <c r="C26" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26">
+        <v>-1600</v>
+      </c>
+      <c r="E26">
+        <v>711</v>
+      </c>
+      <c r="F26">
+        <v>711</v>
+      </c>
+      <c r="G26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B27">
+        <v>2768</v>
+      </c>
+      <c r="C27" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27">
+        <v>-2900</v>
+      </c>
+      <c r="E27">
+        <v>714</v>
+      </c>
+      <c r="F27">
+        <v>714</v>
+      </c>
+      <c r="G27" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B28">
+        <v>8031</v>
+      </c>
+      <c r="C28" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28">
+        <v>-1100</v>
+      </c>
+      <c r="E28">
+        <v>714</v>
+      </c>
+      <c r="F28">
+        <v>714</v>
+      </c>
+      <c r="G28" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B29">
+        <v>7259</v>
+      </c>
+      <c r="C29" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29">
+        <v>1350</v>
+      </c>
+      <c r="E29">
+        <v>715</v>
+      </c>
+      <c r="F29">
+        <v>715</v>
+      </c>
+      <c r="G29" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B30">
+        <v>5595</v>
+      </c>
+      <c r="C30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30">
+        <v>-1000</v>
+      </c>
+      <c r="E30">
+        <v>715</v>
+      </c>
+      <c r="F30">
+        <v>715</v>
+      </c>
+      <c r="G30" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B31">
+        <v>5334</v>
+      </c>
+      <c r="C31" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31">
+        <v>400</v>
+      </c>
+      <c r="E31">
+        <v>716</v>
+      </c>
+      <c r="F31">
+        <v>716</v>
+      </c>
+      <c r="G31" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B32">
+        <v>4004</v>
+      </c>
+      <c r="C32" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32">
+        <v>3900</v>
+      </c>
+      <c r="E32">
+        <v>718</v>
+      </c>
+      <c r="F32">
+        <v>718</v>
+      </c>
+      <c r="G32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" t="s">
+        <v>32</v>
+      </c>
+      <c r="I32" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/articles/yyyymmdd_stockmemo.xlsx
+++ b/articles/yyyymmdd_stockmemo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df63a93e45125bfa/Documents/zenn-contents/public/articles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{534248A1-53E3-4A35-8B78-4CC3CF13077E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{145F813A-78C6-4DC9-9A74-8429BCC317CA}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{534248A1-53E3-4A35-8B78-4CC3CF13077E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95B2637F-8AF7-411F-8D54-FA6081A91F7C}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{3B376C1F-CDE0-4DAE-B15D-C1F4F0EB3929}"/>
+    <workbookView xWindow="21165" yWindow="-15390" windowWidth="20460" windowHeight="14010" xr2:uid="{3B376C1F-CDE0-4DAE-B15D-C1F4F0EB3929}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="44">
   <si>
     <t xml:space="preserve"> コード </t>
   </si>
@@ -81,25 +81,10 @@
     <t xml:space="preserve"> ---- </t>
   </si>
   <si>
-    <t xml:space="preserve"> リコー             </t>
-  </si>
-  <si>
     <t xml:space="preserve">     ロング     </t>
   </si>
   <si>
     <t xml:space="preserve">    ショート    </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 三菱重工業         </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> オリンパス         </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> キャノン           </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 応用地質           </t>
   </si>
   <si>
     <t>ロング</t>
@@ -124,106 +109,76 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve"> 押し目買い</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     07XX </t>
-  </si>
-  <si>
-    <t xml:space="preserve">上昇        </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> レンジ&lt;br&gt;だまし後の&lt;br&gt;上抜け</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 下端反発狙い</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 古野電機           </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 急上昇後の&lt;br&gt;下落</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> レンジ </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 積水ハウス         </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> exitタイ&lt;br&gt;ミング逃し</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 武田製薬           </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> レンジ上限</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ヤマックス         </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 出来高少ない</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 古野電気           </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 高値圏&lt;br&gt;勢い減少</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 損切ライン&lt;br&gt;設定ミス</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 下限狙い</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> アスクル           </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 下落狙い&lt;br&gt;反発(損)切</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 富士通             </t>
   </si>
   <si>
-    <t xml:space="preserve"> 下限狙い&lt;br&gt;下落(損)切</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 寿スピリッツ       </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 下限狙い&lt;br&gt;反発損切</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 日本航空           </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 双日               </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 200株&lt;br&gt;高値圏&lt;br&gt;勢い減少</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 日立製作所         </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 三井物産           </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 三共               </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> アイシン           </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> QPS                </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 日本特殊陶業       </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> レゾナック         </t>
+    <t xml:space="preserve"> REIT-Sosila        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 村田製作所         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 200株 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  215A  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> タイミー           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 東京地下鉄         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> マツキヨココカラCP </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 花王               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">      配当      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 西日本旅客鉄道     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 日本郵政           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 南海電気鉄道       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> クボタ             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 味の素             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> アサヒHD           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 日東電工           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> パナソニックHD     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 第一興商           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 日本取引所G        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 旭化成             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> パンパシHD         </t>
   </si>
 </sst>
 </file>
@@ -591,7 +546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E56617F-AC17-47B0-8938-540D65EDC3F0}">
-  <dimension ref="B2:Q32"/>
+  <dimension ref="B2:Q27"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.4">
@@ -621,7 +576,7 @@
       </c>
       <c r="O2">
         <f>SUM(D4:D49)</f>
-        <v>11784</v>
+        <v>26516</v>
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.4">
@@ -650,738 +605,656 @@
         <v>13</v>
       </c>
       <c r="P3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="Q3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B4">
+        <v>4452</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4">
+        <v>6136</v>
+      </c>
+      <c r="E4">
+        <v>901</v>
+      </c>
+      <c r="F4">
+        <v>901</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
+      </c>
       <c r="O4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="P4">
         <f>COUNTIFS(G4:G50, "*ロング*", D4:D50, "&gt;0")</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q4">
         <f>COUNTIFS(G4:G50, "*ロング*", D4:D50, "&lt;0")</f>
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B5">
+        <v>9021</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5">
+        <v>5700</v>
+      </c>
+      <c r="E5">
+        <v>829</v>
+      </c>
+      <c r="F5">
+        <v>903</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
       <c r="O5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="P5">
         <f>COUNTIFS(G4:G50, "*ショート*", D4:D50, "&gt;0")</f>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q5">
         <f>COUNTIFS(G4:G50, "*ショート*", D4:D50, "&lt;0")</f>
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B6">
-        <v>7733</v>
+        <v>6178</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D6">
-        <v>-2000</v>
+        <v>-200</v>
       </c>
       <c r="E6">
-        <v>701</v>
-      </c>
-      <c r="F6" t="s">
-        <v>26</v>
+        <v>903</v>
+      </c>
+      <c r="F6">
+        <v>917</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B7">
-        <v>7752</v>
+        <v>9044</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D7">
-        <v>-1950</v>
+        <v>-350</v>
       </c>
       <c r="E7">
-        <v>701</v>
+        <v>904</v>
       </c>
       <c r="F7">
-        <v>702</v>
+        <v>904</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B8">
-        <v>7751</v>
+        <v>6326</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D8">
-        <v>-1400</v>
+        <v>450</v>
       </c>
       <c r="E8">
-        <v>701</v>
+        <v>908</v>
       </c>
       <c r="F8">
-        <v>701</v>
+        <v>909</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B9">
-        <v>6814</v>
+        <v>2802</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D9">
-        <v>4500</v>
+        <v>12500</v>
       </c>
       <c r="E9">
-        <v>701</v>
+        <v>910</v>
       </c>
       <c r="F9">
-        <v>701</v>
+        <v>917</v>
       </c>
       <c r="G9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I9" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B10">
-        <v>6814</v>
+        <v>6981</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D10">
-        <v>3500</v>
+        <v>1900</v>
       </c>
       <c r="E10">
-        <v>701</v>
+        <v>910</v>
       </c>
       <c r="F10">
-        <v>701</v>
+        <v>910</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I10" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B11">
-        <v>7752</v>
+        <v>2979</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D11">
-        <v>3650</v>
+        <v>800</v>
       </c>
       <c r="E11">
-        <v>702</v>
+        <v>910</v>
       </c>
       <c r="F11">
-        <v>703</v>
+        <v>922</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B12">
-        <v>1928</v>
+        <v>2502</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D12">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="E12">
-        <v>702</v>
+        <v>911</v>
       </c>
       <c r="F12">
-        <v>702</v>
+        <v>912</v>
       </c>
       <c r="G12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H12" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I12" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B13">
-        <v>4502</v>
+        <v>6702</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D13">
-        <v>3220</v>
+        <v>-2000</v>
       </c>
       <c r="E13">
-        <v>703</v>
+        <v>918</v>
       </c>
       <c r="F13">
-        <v>703</v>
+        <v>918</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I13" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.4">
-      <c r="B14">
-        <v>5285</v>
+      <c r="B14" t="s">
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D14">
-        <v>-3000</v>
+        <v>-1400</v>
       </c>
       <c r="E14">
-        <v>707</v>
+        <v>918</v>
       </c>
       <c r="F14">
-        <v>707</v>
+        <v>919</v>
       </c>
       <c r="G14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H14" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I14" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B15">
-        <v>6814</v>
+        <v>3088</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D15">
-        <v>4000</v>
+        <v>-1500</v>
       </c>
       <c r="E15">
-        <v>707</v>
+        <v>922</v>
       </c>
       <c r="F15">
-        <v>707</v>
+        <v>922</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H15" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I15" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B16">
-        <v>7011</v>
+        <v>6702</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D16">
-        <v>-1700</v>
+        <v>3100</v>
       </c>
       <c r="E16">
-        <v>707</v>
+        <v>924</v>
       </c>
       <c r="F16">
-        <v>707</v>
+        <v>924</v>
       </c>
       <c r="G16" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H16" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I16" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B17">
-        <v>9755</v>
+        <v>6988</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D17">
-        <v>-200</v>
+        <v>6600</v>
       </c>
       <c r="E17">
-        <v>707</v>
+        <v>924</v>
       </c>
       <c r="F17">
-        <v>707</v>
+        <v>924</v>
       </c>
       <c r="G17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H17" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I17" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B18">
-        <v>1928</v>
+        <v>6752</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D18">
-        <v>900</v>
+        <v>-400</v>
       </c>
       <c r="E18">
-        <v>707</v>
+        <v>925</v>
       </c>
       <c r="F18">
-        <v>711</v>
+        <v>925</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I18" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B19">
-        <v>2678</v>
+        <v>7458</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D19">
-        <v>800</v>
+        <v>-150</v>
       </c>
       <c r="E19">
-        <v>707</v>
+        <v>925</v>
       </c>
       <c r="F19">
-        <v>708</v>
+        <v>925</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I19" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B20">
-        <v>6702</v>
+      <c r="B20" t="s">
+        <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D20">
-        <v>500</v>
+        <v>-1700</v>
       </c>
       <c r="E20">
-        <v>709</v>
+        <v>926</v>
       </c>
       <c r="F20">
-        <v>709</v>
+        <v>926</v>
       </c>
       <c r="G20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H20" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I20" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B21">
-        <v>2222</v>
+        <v>8697</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D21">
-        <v>-1050</v>
+        <v>950</v>
       </c>
       <c r="E21">
-        <v>709</v>
+        <v>926</v>
       </c>
       <c r="F21">
-        <v>709</v>
+        <v>926</v>
       </c>
       <c r="G21" t="s">
         <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I21" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B22">
-        <v>2222</v>
+        <v>3088</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D22">
-        <v>4700</v>
+        <v>-700</v>
       </c>
       <c r="E22">
-        <v>709</v>
+        <v>929</v>
       </c>
       <c r="F22">
-        <v>710</v>
+        <v>929</v>
       </c>
       <c r="G22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H22" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I22" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B23">
-        <v>9201</v>
+        <v>3407</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D23">
-        <v>850</v>
+        <v>-100</v>
       </c>
       <c r="E23">
-        <v>710</v>
+        <v>929</v>
       </c>
       <c r="F23">
-        <v>710</v>
+        <v>929</v>
       </c>
       <c r="G23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I23" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B24">
-        <v>2768</v>
+        <v>9023</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D24">
-        <v>1114</v>
+        <v>1560</v>
       </c>
       <c r="E24">
-        <v>711</v>
+        <v>827</v>
       </c>
       <c r="F24">
-        <v>711</v>
+        <v>930</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H24" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I24" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B25">
-        <v>6501</v>
+        <v>6702</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="D25">
-        <v>-2900</v>
+        <v>-4000</v>
       </c>
       <c r="E25">
-        <v>711</v>
+        <v>929</v>
       </c>
       <c r="F25">
-        <v>711</v>
+        <v>930</v>
       </c>
       <c r="G25" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H25" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I25" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B26">
-        <v>8031</v>
+      <c r="B26" t="s">
+        <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="D26">
-        <v>-1600</v>
+        <v>-1000</v>
       </c>
       <c r="E26">
-        <v>711</v>
+        <v>929</v>
       </c>
       <c r="F26">
-        <v>711</v>
+        <v>930</v>
       </c>
       <c r="G26" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H26" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I26" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B27">
-        <v>2768</v>
+        <v>7532</v>
       </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D27">
-        <v>-2900</v>
+        <v>1320</v>
       </c>
       <c r="E27">
-        <v>714</v>
+        <v>930</v>
       </c>
       <c r="F27">
-        <v>714</v>
+        <v>930</v>
       </c>
       <c r="G27" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H27" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I27" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B28">
-        <v>8031</v>
-      </c>
-      <c r="C28" t="s">
-        <v>54</v>
-      </c>
-      <c r="D28">
-        <v>-1100</v>
-      </c>
-      <c r="E28">
-        <v>714</v>
-      </c>
-      <c r="F28">
-        <v>714</v>
-      </c>
-      <c r="G28" t="s">
-        <v>16</v>
-      </c>
-      <c r="H28" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B29">
-        <v>7259</v>
-      </c>
-      <c r="C29" t="s">
-        <v>55</v>
-      </c>
-      <c r="D29">
-        <v>1350</v>
-      </c>
-      <c r="E29">
-        <v>715</v>
-      </c>
-      <c r="F29">
-        <v>715</v>
-      </c>
-      <c r="G29" t="s">
-        <v>15</v>
-      </c>
-      <c r="H29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B30">
-        <v>5595</v>
-      </c>
-      <c r="C30" t="s">
-        <v>56</v>
-      </c>
-      <c r="D30">
-        <v>-1000</v>
-      </c>
-      <c r="E30">
-        <v>715</v>
-      </c>
-      <c r="F30">
-        <v>715</v>
-      </c>
-      <c r="G30" t="s">
-        <v>15</v>
-      </c>
-      <c r="H30" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B31">
-        <v>5334</v>
-      </c>
-      <c r="C31" t="s">
-        <v>57</v>
-      </c>
-      <c r="D31">
-        <v>400</v>
-      </c>
-      <c r="E31">
-        <v>716</v>
-      </c>
-      <c r="F31">
-        <v>716</v>
-      </c>
-      <c r="G31" t="s">
-        <v>16</v>
-      </c>
-      <c r="H31" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B32">
-        <v>4004</v>
-      </c>
-      <c r="C32" t="s">
-        <v>58</v>
-      </c>
-      <c r="D32">
-        <v>3900</v>
-      </c>
-      <c r="E32">
-        <v>718</v>
-      </c>
-      <c r="F32">
-        <v>718</v>
-      </c>
-      <c r="G32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H32" t="s">
-        <v>32</v>
-      </c>
-      <c r="I32" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/articles/yyyymmdd_stockmemo.xlsx
+++ b/articles/yyyymmdd_stockmemo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df63a93e45125bfa/Documents/zenn-contents/public/articles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="144" documentId="8_{534248A1-53E3-4A35-8B78-4CC3CF13077E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2C3A382-E3E4-430B-BA6E-EA40D9F5A6EA}"/>
+  <xr:revisionPtr revIDLastSave="157" documentId="8_{534248A1-53E3-4A35-8B78-4CC3CF13077E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C65A8F2-5920-476D-B1AA-5036D7BB3D09}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{3B376C1F-CDE0-4DAE-B15D-C1F4F0EB3929}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="63">
   <si>
     <t xml:space="preserve"> コード </t>
   </si>
@@ -470,6 +470,45 @@
   </si>
   <si>
     <t>売りでエントリーする。（誤差３）</t>
+  </si>
+  <si>
+    <t>値動きが激しい場合は、</t>
+    <rPh sb="0" eb="2">
+      <t>ネウゴ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ハゲ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>損切幅15でエントリーする</t>
+    <rPh sb="0" eb="3">
+      <t>ソンギリハバ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（普段のチャートが5分足系の銘柄など）</t>
+    <rPh sb="1" eb="3">
+      <t>フダン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>アシ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>メイガラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -24706,6 +24745,417 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>29536</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>96127</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="図 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F630A2EE-80D6-5255-46D9-6F5A8891AF35}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11068050" y="18573750"/>
+          <a:ext cx="6887536" cy="6287377"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="テキスト ボックス 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53D5AFE0-61AF-4A21-BD4F-8390037BB261}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15801975" y="20916900"/>
+          <a:ext cx="552450" cy="600075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>①</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>409574</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="正方形/長方形 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEE7CCCC-C1AD-489E-8476-36181919C370}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15954375" y="21393150"/>
+          <a:ext cx="323849" cy="1123950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="テキスト ボックス 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8E6D530-A3B7-4EB0-A2EF-66C6B4CD45B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16468725" y="20916900"/>
+          <a:ext cx="552450" cy="600075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>②</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>209549</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>133349</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="正方形/長方形 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29B8D008-E09E-48B1-A224-52DE2E7782F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16297275" y="21402674"/>
+          <a:ext cx="609600" cy="1114425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="テキスト ボックス 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA9F0640-8211-4113-85D6-EF16F13D04EB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12496800" y="21145500"/>
+          <a:ext cx="3676650" cy="409575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>損切ライン</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(+10)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>に到達してしまっている</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800" b="0">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -25841,6 +26291,21 @@
         <v>52</v>
       </c>
     </row>
+    <row r="93" spans="13:13" x14ac:dyDescent="0.4">
+      <c r="M93" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="94" spans="13:13" x14ac:dyDescent="0.4">
+      <c r="M94" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="95" spans="13:13" x14ac:dyDescent="0.4">
+      <c r="M95" t="s">
+        <v>62</v>
+      </c>
+    </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A114" s="2" t="s">
         <v>49</v>
